--- a/reports/川田_sample_5_answer_レース結果報告.xlsx
+++ b/reports/川田_sample_5_answer_レース結果報告.xlsx
@@ -35,6 +35,7 @@
     <font>
       <b val="1"/>
       <color rgb="000000FF"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="5">
@@ -58,8 +59,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00FFF8DC"/>
+        <bgColor rgb="00FFF8DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,10 +82,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -93,6 +97,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -460,8 +467,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -484,828 +502,667 @@
           <t>判定</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr"/>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>問題</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>解答</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>正解</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
       </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="2" t="n"/>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="2" t="n"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="2" t="n"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="2" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="2" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="2" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" s="3" t="n">
         <v>27</v>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="H8" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="2" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="H9" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="2" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="2" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="2" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>31</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="2" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="2" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="2" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="2" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>&lt;span class="ok"&gt;⭕&lt;/span&gt;</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="2" t="n"/>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>⭕</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
